--- a/scripts/Provincial_Tools/tbl_sql_classify.xlsx
+++ b/scripts/Provincial_Tools/tbl_sql_classify.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\T\git\p3t_ArcGIS_Pro_Tools\scripts\Provincial_Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D80FB2-276F-4299-8B86-1A347256B6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5E7B5C-7B5F-467A-AE2E-7DF1136883B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="552" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40080" yWindow="600" windowWidth="28320" windowHeight="16470" tabRatio="552" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instruction" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2960" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2966" uniqueCount="723">
   <si>
     <t>RECNO</t>
   </si>
@@ -1975,24 +1975,6 @@
   </si>
   <si>
     <t>(Ce &gt;= 20 And EcoGrp = 'UplCe') Or ((Ce &gt;= 40 And Bf &lt;= 10 And (Pr + Pw + Pj + Sw + Bf + PO+PT+PL) &gt;= 20 And AllCon &gt;= 70) And (EcoGrp &lt;&gt; 'ConLow'))</t>
-  </si>
-  <si>
-    <t>(LGFU='PWDOM' AND AGE&lt;10) OR 
-(LGFU='PRDOM' AND AGE&lt;10) OR 
-(LGFU='PRWMX' AND AGE&lt;10) OR 
-(LGFU='OCLOW' AND AGE&lt;10) OR 
-(LGFU='SBLOW' AND AGE&lt;10) OR 
-(LGFU='SbDom' AND AGE&lt;10) OR 
-(LGFU='PJDom' AND AGE&lt;10) OR 
-(LGFU='PODOM' AND AGE&lt;5) OR 
-(LGFU='BWDOM' AND AGE&lt;5) OR 
-(LGFU='OTHHD' AND AGE&lt;5) OR 
-(LGFU='SBMX1' AND AGE&lt;10) OR 
-(LGFU='PJMX1' AND AGE&lt;10) OR 
-(LGFU='BFDOM' AND AGE&lt;5) OR 
-(LGFU='CONMX' AND AGE&lt;10) OR 
-(LGFU='HRDOM' AND AGE&lt;5) OR 
-(LGFU='HRDMX' AND AGE&lt;5)</t>
   </si>
   <si>
     <t>(LGFU='PWDOM' AND AGE&gt;=10 AND AGE&lt;=19) OR 
@@ -2029,24 +2011,6 @@
 (LGFU='CONMX' AND AGE&gt;=30 AND AGE&lt;=69) OR
 (LGFU='HRDOM' AND AGE&gt;=10 AND AGE&lt;=59) OR
 (LGFU='HRDMX' AND AGE&gt;=10 AND AGE&lt;=59)</t>
-  </si>
-  <si>
-    <t>(LGFU='PWDOM' AND AGE&gt;=80 AND AGE&lt;=129) OR
-(LGFU='PRDOM' AND AGE&gt;=80 AND AGE&lt;=149) OR
-(LGFU='PRWMX' AND AGE&gt;=80 AND AGE&lt;=139) OR
-(LGFU='OCLOW' AND AGE&gt;=70 AND AGE&lt;=119) OR
-(LGFU='SBLOW' AND AGE&gt;=70 AND AGE&lt;=159) OR
-(LGFU='SbDom' AND AGE&gt;=70 AND AGE&lt;=119) OR
-(LGFU='PJDom' AND AGE&gt;=70 AND AGE&lt;=99) OR
-(LGFU='PODom' AND AGE&gt;=60 AND AGE&lt;=99) OR
-(LGFU='BWDOM' AND AGE&gt;=50 AND AGE&lt;=109) OR
-(LGFU='OTHHD' AND AGE&gt;=60 AND AGE&lt;=99) OR
-(LGFU='SBMX1' AND AGE&gt;=70 AND AGE&lt;=109) OR
-(LGFU='PJMX1' AND AGE&gt;=70 AND AGE&lt;=99) OR
-(LGFU='BFDOM' AND AGE&gt;=60 AND AGE&lt;=79) OR
-(LGFU='CONMX' AND AGE&gt;=70 AND AGE&lt;=109) OR
-(LGFU='HRDOM' AND AGE&gt;=60 AND AGE&lt;=99) OR
-(LGFU='HRDMX' AND AGE&gt;=60 AND AGE&lt;=109)</t>
   </si>
   <si>
     <t>(LGFU='PWDOM' AND AGE&gt;129) OR
@@ -2458,6 +2422,63 @@
   </si>
   <si>
     <t>had chat with J. Mucha - HRDOM may need to move to POP?</t>
+  </si>
+  <si>
+    <t>(LGFU='PWDOM' AND AGE&lt;10) OR 
+(LGFU='PRDOM' AND AGE&lt;10) OR 
+(LGFU='PRWMX' AND AGE&lt;10) OR 
+(LGFU='OCLOW' AND AGE&lt;10) OR 
+(LGFU='SBLOW' AND AGE&lt;10) OR 
+(LGFU='SBDOM' AND AGE&lt;10) OR 
+(LGFU='PJDOM' AND AGE&lt;10) OR 
+(LGFU='PODOM' AND AGE&lt;5) OR 
+(LGFU='BWDOM' AND AGE&lt;5) OR 
+(LGFU='OTHHD' AND AGE&lt;5) OR 
+(LGFU='SBMX1' AND AGE&lt;10) OR 
+(LGFU='PJMX1' AND AGE&lt;10) OR 
+(LGFU='BFDOM' AND AGE&lt;5) OR 
+(LGFU='CONMX' AND AGE&lt;10) OR 
+(LGFU='HRDOM' AND AGE&lt;5) OR 
+(LGFU='HRDMX' AND AGE&lt;5)</t>
+  </si>
+  <si>
+    <t>(LGFU='PWDOM' AND AGE&gt;=80 AND AGE&lt;=129) OR
+(LGFU='PRDOM' AND AGE&gt;=80 AND AGE&lt;=149) OR
+(LGFU='PRWMX' AND AGE&gt;=80 AND AGE&lt;=139) OR
+(LGFU='OCLOW' AND AGE&gt;=70 AND AGE&lt;=119) OR
+(LGFU='SBLOW' AND AGE&gt;=70 AND AGE&lt;=159) OR
+(LGFU='SBDOM' AND AGE&gt;=70 AND AGE&lt;=119) OR
+(LGFU='PJDOM' AND AGE&gt;=70 AND AGE&lt;=99) OR
+(LGFU='PODOM' AND AGE&gt;=60 AND AGE&lt;=99) OR
+(LGFU='BWDOM' AND AGE&gt;=50 AND AGE&lt;=109) OR
+(LGFU='OTHHD' AND AGE&gt;=60 AND AGE&lt;=99) OR
+(LGFU='SBMX1' AND AGE&gt;=70 AND AGE&lt;=109) OR
+(LGFU='PJMX1' AND AGE&gt;=70 AND AGE&lt;=99) OR
+(LGFU='BFDOM' AND AGE&gt;=60 AND AGE&lt;=79) OR
+(LGFU='CONMX' AND AGE&gt;=70 AND AGE&lt;=109) OR
+(LGFU='HRDOM' AND AGE&gt;=60 AND AGE&lt;=99) OR
+(LGFU='HRDMX' AND AGE&gt;=60 AND AGE&lt;=109)</t>
+  </si>
+  <si>
+    <t>rewrote to all uppercase</t>
+  </si>
+  <si>
+    <t>LGDS='I' AND LGFU IN ('BFDOM', 'CONMX', 'UPLCE', 'PJDOM', 'SBDOM', 'SBLOW', 'OCLOW', 'PJMX1', 'PRWMX', 'SBMX1')</t>
+  </si>
+  <si>
+    <t>LGDS='I' AND LGFU IN ('BWDOM', 'HRDMX', 'HRDOM', 'PODOM', 'OTHHD')</t>
+  </si>
+  <si>
+    <t>(LGDS='M' OR LGDS='L') AND LGFU='BFDOM'</t>
+  </si>
+  <si>
+    <t>(LGDS='M' OR LGDS='L') AND (LGFU='SBLOW' OR LGFU='OCLOW')</t>
+  </si>
+  <si>
+    <t>(LGDS='M' OR LGDS='L') AND (LGFU='BWDOM' OR LGFU='HRDMX' OR LGFU='HRDOM' OR LGFU='OTHHD' OR LGFU='PODOM')</t>
+  </si>
+  <si>
+    <t>(LGDS='M' OR LGDS='L') AND LGFU IN ('CONMX', 'PJDOM', 'UPLCE', 'PJMX1', 'PRWMX', 'SBDOM', 'SBMX1')</t>
   </si>
 </sst>
 </file>
@@ -2669,11 +2690,19 @@
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-CA" sz="1100"/>
+            <a:rPr lang="en-CA" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>Any changes made on this xlsx doesn't impact</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-CA" sz="1100" baseline="0"/>
+            <a:rPr lang="en-CA" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t> the tool unless you export this as csv file.</a:t>
           </a:r>
         </a:p>
@@ -2836,19 +2865,104 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F90BB50-DC12-D4E4-0A4D-E14E4B056A3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="4991100"/>
+          <a:ext cx="6238875" cy="2390775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200"/>
+            <a:t>Change Log</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200"/>
+            <a:t>2026 03 03</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200"/>
+            <a:t>NWR LGDS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+            <a:t> and LGCLS - some of the queries were origainlly written in mix of upper and lower case. I rewrote them all with uppercase.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{78662066-8961-40A1-8222-90158F51F698}" name="Table2" displayName="Table2" ref="A1:I204" totalsRowShown="0">
-  <autoFilter ref="A1:I204" xr:uid="{78662066-8961-40A1-8222-90158F51F698}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="PFT"/>
-        <filter val="SFU"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I204" xr:uid="{78662066-8961-40A1-8222-90158F51F698}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I204">
     <sortCondition ref="B2:B204"/>
     <sortCondition ref="C2:C204"/>
@@ -3224,7 +3338,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>600</v>
       </c>
@@ -3244,7 +3358,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>601</v>
       </c>
@@ -3264,7 +3378,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>602</v>
       </c>
@@ -3284,7 +3398,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>603</v>
       </c>
@@ -3304,7 +3418,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>604</v>
       </c>
@@ -3321,13 +3435,13 @@
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H6" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>810</v>
       </c>
@@ -3347,7 +3461,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>811</v>
       </c>
@@ -3367,7 +3481,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>812</v>
       </c>
@@ -3387,7 +3501,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>813</v>
       </c>
@@ -3407,7 +3521,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>814</v>
       </c>
@@ -3427,7 +3541,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>815</v>
       </c>
@@ -3447,7 +3561,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>816</v>
       </c>
@@ -3467,7 +3581,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>817</v>
       </c>
@@ -3487,7 +3601,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="375" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="375" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>680</v>
       </c>
@@ -3504,10 +3618,10 @@
         <v>86</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="375" hidden="1" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="375" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>681</v>
       </c>
@@ -3524,10 +3638,10 @@
         <v>103</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="375" hidden="1" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="375" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>682</v>
       </c>
@@ -3544,10 +3658,10 @@
         <v>120</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="375" hidden="1" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="375" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>683</v>
       </c>
@@ -3564,10 +3678,10 @@
         <v>137</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="375" hidden="1" x14ac:dyDescent="0.25">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="375" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>684</v>
       </c>
@@ -3584,10 +3698,10 @@
         <v>154</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>805</v>
       </c>
@@ -3607,7 +3721,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>650</v>
       </c>
@@ -3627,7 +3741,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>651</v>
       </c>
@@ -3647,7 +3761,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>652</v>
       </c>
@@ -3667,7 +3781,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>653</v>
       </c>
@@ -3687,7 +3801,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>654</v>
       </c>
@@ -3707,7 +3821,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>655</v>
       </c>
@@ -3727,7 +3841,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>656</v>
       </c>
@@ -3747,7 +3861,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>657</v>
       </c>
@@ -3767,7 +3881,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>658</v>
       </c>
@@ -3787,7 +3901,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>659</v>
       </c>
@@ -3807,7 +3921,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>660</v>
       </c>
@@ -3827,7 +3941,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>661</v>
       </c>
@@ -3847,7 +3961,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>662</v>
       </c>
@@ -3867,7 +3981,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>663</v>
       </c>
@@ -3887,7 +4001,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>664</v>
       </c>
@@ -3907,7 +4021,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>665</v>
       </c>
@@ -3927,7 +4041,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>666</v>
       </c>
@@ -3947,7 +4061,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>667</v>
       </c>
@@ -3967,7 +4081,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>668</v>
       </c>
@@ -3987,7 +4101,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>669</v>
       </c>
@@ -4007,7 +4121,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>670</v>
       </c>
@@ -4027,7 +4141,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>671</v>
       </c>
@@ -4047,7 +4161,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>672</v>
       </c>
@@ -4067,7 +4181,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>673</v>
       </c>
@@ -4087,7 +4201,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>674</v>
       </c>
@@ -4107,7 +4221,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>675</v>
       </c>
@@ -4127,7 +4241,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>676</v>
       </c>
@@ -4862,7 +4976,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>300</v>
       </c>
@@ -4885,7 +4999,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>301</v>
       </c>
@@ -4908,7 +5022,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>302</v>
       </c>
@@ -4931,7 +5045,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>303</v>
       </c>
@@ -4954,7 +5068,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>304</v>
       </c>
@@ -4971,16 +5085,16 @@
         <v>16</v>
       </c>
       <c r="F87" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H87" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="I87" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>480</v>
       </c>
@@ -5000,7 +5114,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>481</v>
       </c>
@@ -5020,7 +5134,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>482</v>
       </c>
@@ -5040,7 +5154,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>483</v>
       </c>
@@ -5060,7 +5174,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>484</v>
       </c>
@@ -5080,7 +5194,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>485</v>
       </c>
@@ -5100,7 +5214,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>486</v>
       </c>
@@ -5120,7 +5234,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>487</v>
       </c>
@@ -5140,7 +5254,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>488</v>
       </c>
@@ -5160,7 +5274,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="225" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>442</v>
       </c>
@@ -5177,13 +5291,13 @@
         <v>137</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G97" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" ht="225" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>456</v>
       </c>
@@ -5200,13 +5314,13 @@
         <v>154</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G98" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="225" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>400</v>
       </c>
@@ -5223,13 +5337,13 @@
         <v>86</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="G99" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="225" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>414</v>
       </c>
@@ -5246,13 +5360,13 @@
         <v>103</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G100" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="225" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>428</v>
       </c>
@@ -5269,13 +5383,13 @@
         <v>120</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G101" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>350</v>
       </c>
@@ -5292,13 +5406,13 @@
         <v>212</v>
       </c>
       <c r="F102" t="s">
+        <v>697</v>
+      </c>
+      <c r="I102" t="s">
         <v>699</v>
       </c>
-      <c r="I102" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>351</v>
       </c>
@@ -5315,13 +5429,13 @@
         <v>214</v>
       </c>
       <c r="F103" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="I103" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>356</v>
       </c>
@@ -5341,10 +5455,10 @@
         <v>604</v>
       </c>
       <c r="I104" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>359</v>
       </c>
@@ -5361,13 +5475,13 @@
         <v>218</v>
       </c>
       <c r="F105" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="I105" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>360</v>
       </c>
@@ -5384,13 +5498,13 @@
         <v>220</v>
       </c>
       <c r="F106" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="I106" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>362</v>
       </c>
@@ -5407,13 +5521,13 @@
         <v>222</v>
       </c>
       <c r="F107" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="I107" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>364</v>
       </c>
@@ -5430,13 +5544,13 @@
         <v>224</v>
       </c>
       <c r="F108" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="I108" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>365</v>
       </c>
@@ -5453,13 +5567,13 @@
         <v>226</v>
       </c>
       <c r="F109" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="I109" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>367</v>
       </c>
@@ -5476,13 +5590,13 @@
         <v>228</v>
       </c>
       <c r="F110" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="I110" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>208</v>
       </c>
@@ -5496,13 +5610,13 @@
         <v>230</v>
       </c>
       <c r="F111" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="I111" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>208</v>
       </c>
@@ -5516,13 +5630,13 @@
         <v>232</v>
       </c>
       <c r="F112" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="I112" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>208</v>
       </c>
@@ -5536,13 +5650,13 @@
         <v>234</v>
       </c>
       <c r="F113" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="I113" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
         <v>208</v>
       </c>
@@ -5556,13 +5670,13 @@
         <v>236</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="I114" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>208</v>
       </c>
@@ -5576,10 +5690,10 @@
         <v>241</v>
       </c>
       <c r="F115" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="I115" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -5625,7 +5739,7 @@
         <v>352</v>
       </c>
       <c r="G117" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -5645,13 +5759,13 @@
         <v>196</v>
       </c>
       <c r="F118" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="G118" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H118" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -5674,7 +5788,7 @@
         <v>602</v>
       </c>
       <c r="G119" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
@@ -5697,7 +5811,7 @@
         <v>603</v>
       </c>
       <c r="G120" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -5766,7 +5880,7 @@
         <v>604</v>
       </c>
       <c r="G123" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -5792,7 +5906,7 @@
         <v>571</v>
       </c>
       <c r="I124" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -5815,10 +5929,10 @@
         <v>572</v>
       </c>
       <c r="H125" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I125" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -5844,10 +5958,10 @@
         <v>573</v>
       </c>
       <c r="H126" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I126" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -5867,16 +5981,16 @@
         <v>216</v>
       </c>
       <c r="F127" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G127" t="s">
         <v>574</v>
       </c>
       <c r="H127" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="I127" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -5899,10 +6013,10 @@
         <v>575</v>
       </c>
       <c r="H128" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I128" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
@@ -5928,10 +6042,10 @@
         <v>587</v>
       </c>
       <c r="H129" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I129" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
@@ -5951,16 +6065,16 @@
         <v>220</v>
       </c>
       <c r="F130" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G130" t="s">
         <v>576</v>
       </c>
       <c r="H130" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="I130" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
@@ -5980,16 +6094,16 @@
         <v>222</v>
       </c>
       <c r="F131" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="G131" t="s">
         <v>577</v>
       </c>
       <c r="H131" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="I131" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
@@ -6015,10 +6129,10 @@
         <v>578</v>
       </c>
       <c r="H132" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I132" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
@@ -6032,19 +6146,19 @@
         <v>10</v>
       </c>
       <c r="E133" t="s">
+        <v>690</v>
+      </c>
+      <c r="F133" t="s">
+        <v>693</v>
+      </c>
+      <c r="G133" t="s">
         <v>692</v>
       </c>
-      <c r="F133" t="s">
-        <v>695</v>
-      </c>
-      <c r="G133" t="s">
-        <v>694</v>
-      </c>
       <c r="H133" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="I133" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
@@ -6070,10 +6184,10 @@
         <v>577</v>
       </c>
       <c r="H134" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I134" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
@@ -6099,10 +6213,10 @@
         <v>579</v>
       </c>
       <c r="H135" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I135" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
@@ -6128,10 +6242,10 @@
         <v>580</v>
       </c>
       <c r="H136" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I136" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
@@ -6157,10 +6271,10 @@
         <v>581</v>
       </c>
       <c r="H137" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I137" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
@@ -6186,10 +6300,10 @@
         <v>582</v>
       </c>
       <c r="H138" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I138" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
@@ -6209,16 +6323,16 @@
         <v>583</v>
       </c>
       <c r="F139" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G139" t="s">
         <v>588</v>
       </c>
       <c r="H139" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I139" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
@@ -6238,16 +6352,16 @@
         <v>584</v>
       </c>
       <c r="F140" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G140" t="s">
         <v>589</v>
       </c>
       <c r="H140" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I140" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
@@ -6273,7 +6387,7 @@
         <v>590</v>
       </c>
       <c r="I141" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
@@ -6299,10 +6413,10 @@
         <v>591</v>
       </c>
       <c r="I142" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>1</v>
       </c>
@@ -6325,7 +6439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2</v>
       </c>
@@ -6348,7 +6462,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>3</v>
       </c>
@@ -6371,7 +6485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>4</v>
       </c>
@@ -6394,7 +6508,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>5</v>
       </c>
@@ -6411,13 +6525,13 @@
         <v>16</v>
       </c>
       <c r="F147" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H147" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>128</v>
       </c>
@@ -6434,10 +6548,10 @@
         <v>177</v>
       </c>
       <c r="F148" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>129</v>
       </c>
@@ -6454,10 +6568,13 @@
         <v>179</v>
       </c>
       <c r="F149" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>717</v>
+      </c>
+      <c r="H149" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>130</v>
       </c>
@@ -6474,10 +6591,13 @@
         <v>181</v>
       </c>
       <c r="F150" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>718</v>
+      </c>
+      <c r="H150" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>131</v>
       </c>
@@ -6494,10 +6614,13 @@
         <v>183</v>
       </c>
       <c r="F151" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+      <c r="H151" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>132</v>
       </c>
@@ -6514,10 +6637,10 @@
         <v>185</v>
       </c>
       <c r="F152" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>133</v>
       </c>
@@ -6534,10 +6657,10 @@
         <v>187</v>
       </c>
       <c r="F153" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>134</v>
       </c>
@@ -6554,10 +6677,13 @@
         <v>189</v>
       </c>
       <c r="F154" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" ht="240" hidden="1" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="H154" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="240" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
         <v>6</v>
       </c>
@@ -6571,10 +6697,13 @@
         <v>86</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" ht="240" hidden="1" x14ac:dyDescent="0.25">
+        <v>714</v>
+      </c>
+      <c r="H155" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="240" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>59</v>
       </c>
@@ -6591,10 +6720,10 @@
         <v>103</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" ht="240" hidden="1" x14ac:dyDescent="0.25">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="240" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>75</v>
       </c>
@@ -6611,10 +6740,10 @@
         <v>120</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" ht="240" hidden="1" x14ac:dyDescent="0.25">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="240" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>91</v>
       </c>
@@ -6631,10 +6760,13 @@
         <v>137</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" ht="240" hidden="1" x14ac:dyDescent="0.25">
+        <v>715</v>
+      </c>
+      <c r="H158" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="240" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>107</v>
       </c>
@@ -6651,10 +6783,10 @@
         <v>154</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>29</v>
       </c>
@@ -6674,7 +6806,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>30</v>
       </c>
@@ -6694,7 +6826,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>31</v>
       </c>
@@ -6714,7 +6846,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>32</v>
       </c>
@@ -6734,7 +6866,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>33</v>
       </c>
@@ -6754,7 +6886,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>34</v>
       </c>
@@ -6774,7 +6906,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>35</v>
       </c>
@@ -6794,7 +6926,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>36</v>
       </c>
@@ -6814,7 +6946,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>37</v>
       </c>
@@ -6834,7 +6966,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>38</v>
       </c>
@@ -6854,7 +6986,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>39</v>
       </c>
@@ -6874,7 +7006,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>40</v>
       </c>
@@ -6894,7 +7026,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>41</v>
       </c>
@@ -6914,7 +7046,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>42</v>
       </c>
@@ -7034,7 +7166,7 @@
         <v>201</v>
       </c>
       <c r="I178" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
@@ -17392,14 +17524,14 @@
         <v>216</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="F5" s="10"/>
       <c r="G5" s="10" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -17456,12 +17588,12 @@
         <v>220</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="8" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -17478,14 +17610,14 @@
         <v>222</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="10" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -17502,12 +17634,12 @@
         <v>224</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="8" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -17564,11 +17696,11 @@
         <v>228</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="10" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="H13" s="11"/>
     </row>
@@ -17606,12 +17738,12 @@
         <v>232</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="11" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -17628,12 +17760,12 @@
         <v>234</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="8" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="90" x14ac:dyDescent="0.25">
@@ -17650,14 +17782,14 @@
         <v>236</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="10" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">

--- a/scripts/Provincial_Tools/tbl_sql_classify.xlsx
+++ b/scripts/Provincial_Tools/tbl_sql_classify.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\T\git\p3t_ArcGIS_Pro_Tools\scripts\Provincial_Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5E7B5C-7B5F-467A-AE2E-7DF1136883B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB6BFC9-7816-4335-AD14-1C2FF31CF629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40080" yWindow="600" windowWidth="28320" windowHeight="16470" tabRatio="552" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="552" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instruction" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2966" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="724">
   <si>
     <t>RECNO</t>
   </si>
@@ -1969,9 +1969,6 @@
   </si>
   <si>
     <t>(MH+AW+BD+BE+CH+IW+QR+YB+OW+OB+HE+EX&gt;=50) AND (PO+PT+PL+PB+BW+BF&lt;=30) AND (SC&lt;=2)</t>
-  </si>
-  <si>
-    <t>can be deleted unless NER LGFU actually has PW1</t>
   </si>
   <si>
     <t>(Ce &gt;= 20 And EcoGrp = 'UplCe') Or ((Ce &gt;= 40 And Bf &lt;= 10 And (Pr + Pw + Pj + Sw + Bf + PO+PT+PL) &gt;= 20 And AllCon &gt;= 70) And (EcoGrp &lt;&gt; 'ConLow'))</t>
@@ -2029,91 +2026,6 @@
 (LGFU='CONMX' AND AGE&gt;109) OR
 (LGFU='HRDOM' AND AGE&gt;99) OR
 (LGFU='HRDMX' AND AGE&gt;109)</t>
-  </si>
-  <si>
-    <t>(LGFU='PW1' AND AGE&gt;=0 AND AGE&lt;15) OR
-(LGFU='PR1' AND AGE&gt;0 AND AGE&lt;15) OR
-(LGFU='PRW' AND AGE&gt;=0 AND AGE&lt;15) OR
-(LGFU='LC1' AND AGE&gt;=0 AND AGE&lt;20) OR
-(LGFU='SB1' AND AGE&gt;=0 AND AGE&lt;20) OR
-(LGFU='SP1' AND AGE&gt;=0 AND AGE&lt;15) OR
-(LGFU='PJ1' AND AGE&gt;=0 AND AGE&lt;10) OR
-(LGFU='PO1' AND AGE&gt;=0 AND AGE&lt;10) OR
-(LGFU='BW1' AND AGE&gt;=0 AND AGE&lt;10) OR
-(LGFU='LH1' AND AGE&gt;=0 AND AGE&lt;10) OR
-(LGFU='MW1' AND AGE&gt;0 AND AGE&lt;10) OR
-(LGFU='PJ2' AND AGE&gt;=0 AND AGE&lt;10) OR
-(LGFU='SF1' AND AGE&gt;=0 AND AGE&lt;15) OR
-(LGFU='MW2' AND AGE&gt;=0 AND AGE&lt;10) OR
-(LGFU='BOG' AND AGE&gt;=0 AND AGE&lt;20)</t>
-  </si>
-  <si>
-    <t>(LGFU='PW1' AND AGE&gt;=15 AND AGE&lt;=39) OR
-(LGFU='PR1' AND AGE&gt;=15 AND AGE&lt;=39) OR
-(LGFU='PRW' AND AGE&gt;=15 AND AGE&lt;=39) OR
-(LGFU='LC1' AND AGE&gt;=20 AND AGE&lt;=39) OR
-(LGFU='SB1' AND AGE&gt;=20 AND AGE&lt;=39) OR
-(LGFU='SP1' AND AGE&gt;=15 AND AGE&lt;=39) OR
-(LGFU='PJ1' AND AGE&gt;=10 AND AGE&lt;=29) OR
-(LGFU='PO1' AND AGE&gt;=10 AND AGE&lt;=29) OR
-(LGFU='BW1' AND AGE&gt;=10 AND AGE&lt;=29) OR
-(LGFU='LH1' AND AGE&gt;=10 AND AGE&lt;=29) OR
-(LGFU='MW1' AND AGE&gt;=10 AND AGE&lt;=29) OR
-(LGFU='PJ2' AND AGE&gt;=10 AND AGE&lt;=29) OR
-(LGFU='SF1' AND AGE&gt;=15 AND AGE&lt;=39) OR
-(LGFU='MW2' AND AGE&gt;=10 AND AGE&lt;=29) OR
-(LGFU='BOG' AND AGE&gt;=20 AND AGE&lt;=39)</t>
-  </si>
-  <si>
-    <t>(LGFU='PW1' AND AGE&gt;=40 AND AGE&lt;=79) OR
-(LGFU='PR1' AND AGE&gt;=40 AND AGE&lt;=79) OR
-(LGFU='PRW' AND AGE&gt;=40 AND AGE&lt;=79) OR
-(LGFU='LC1' AND AGE&gt;=40 AND AGE&lt;=79) OR
-(LGFU='SB1' AND AGE&gt;=40 AND AGE&lt;=79) OR
-(LGFU='SP1' AND AGE&gt;=40 AND AGE&lt;=79) OR
-(LGFU='PJ1' AND AGE&gt;=30 AND AGE&lt;=69) OR
-(LGFU='PO1' AND AGE&gt;=30 AND AGE&lt;=59) OR
-(LGFU='BW1' AND AGE&gt;=30 AND AGE&lt;=69) OR
-(LGFU='LH1' AND AGE&gt;=30 AND AGE&lt;=69) OR
-(LGFU='MW1' AND AGE&gt;=30 AND AGE&lt;=69) OR
-(LGFU='PJ2' AND AGE&gt;=30 AND AGE&lt;=69) OR
-(LGFU='SF1' AND AGE&gt;=40 AND AGE&lt;=79) OR
-(LGFU='MW2' AND AGE&gt;=30 AND AGE&lt;=69) OR
-(LGFU='BOG' AND AGE&gt;=40 AND AGE&lt;=79)</t>
-  </si>
-  <si>
-    <t>(LGFU='PW1' AND AGE&gt;=80 AND AGE&lt;=129) OR
-(LGFU='PR1' AND AGE&gt;=80 AND AGE&lt;=129) OR
-(LGFU='PRW' AND AGE&gt;=80 AND AGE&lt;=129) OR
-(LGFU='LC1' AND AGE&gt;=80 AND AGE&lt;=119) OR
-(LGFU='SB1' AND AGE&gt;=80 AND AGE&lt;=119) OR
-(LGFU='SP1' AND AGE&gt;=80 AND AGE&lt;=109) OR
-(LGFU='PJ1' AND AGE&gt;=70 AND AGE&lt;=109) OR
-(LGFU='PO1' AND AGE&gt;=60 AND AGE&lt;=89) OR
-(LGFU='BW1' AND AGE&gt;=70 AND AGE&lt;=89) OR
-(LGFU='LH1' AND AGE&gt;=70 AND AGE&lt;=99) OR
-(LGFU='MW1' AND AGE&gt;=70 AND AGE&lt;=99) OR
-(LGFU='PJ2' AND AGE&gt;=70 AND AGE&lt;=109) OR
-(LGFU='SF1' AND AGE&gt;=80 AND AGE&lt;=109) OR
-(LGFU='MW2' AND AGE&gt;=70 AND AGE&lt;=99) OR
-(LGFU='BOG' AND AGE&gt;=80 AND AGE&lt;=119)</t>
-  </si>
-  <si>
-    <t>(LGFU='PW1' AND AGE&gt;129) OR
-(LGFU='PR1' AND AGE&gt;129) OR
-(LGFU='PRW' AND AGE&gt;129) OR
-(LGFU='LC1' AND AGE&gt;=120) OR
-(LGFU='SB1' AND AGE&gt;=120) OR
-(LGFU='SP1' AND AGE&gt;=110) OR
-(LGFU='PJ1' AND AGE&gt;=110) OR
-(LGFU='PO1' AND AGE&gt;89) OR
-(LGFU='BW1' AND AGE&gt;89) OR
-(LGFU='LH1' AND AGE&gt;99) OR
-(LGFU='MW1' AND AGE&gt;99) OR
-(LGFU='PJ2' AND AGE&gt;109) OR
-(LGFU='SF1' AND AGE&gt;109) OR
-(LGFU='MW2' AND AGE&gt;99) OR
-(LGFU='BOG' AND AGE&gt;=120)</t>
   </si>
   <si>
     <t>(LGFU='PR' AND AGE&lt;=14) OR
@@ -2479,6 +2391,97 @@
   </si>
   <si>
     <t>(LGDS='M' OR LGDS='L') AND LGFU IN ('CONMX', 'PJDOM', 'UPLCE', 'PJMX1', 'PRWMX', 'SBDOM', 'SBMX1')</t>
+  </si>
+  <si>
+    <t>(LGFU='SBOG')</t>
+  </si>
+  <si>
+    <t>(LGFU='PW1' AND AGE&gt;=80 AND AGE&lt;=129) OR
+(LGFU='PR1' AND AGE&gt;=80 AND AGE&lt;=129) OR
+(LGFU='PRW' AND AGE&gt;=80 AND AGE&lt;=129) OR
+(LGFU='LC1' AND AGE&gt;=80 AND AGE&lt;=119) OR
+(LGFU='SB1' AND AGE&gt;=80 AND AGE&lt;=119) OR
+(LGFU='SP1' AND AGE&gt;=80 AND AGE&lt;=109) OR
+(LGFU='PJ1' AND AGE&gt;=70 AND AGE&lt;=109) OR
+(LGFU='PO1' AND AGE&gt;=60 AND AGE&lt;=89) OR
+(LGFU='BW1' AND AGE&gt;=70 AND AGE&lt;=89) OR
+(LGFU='LH1' AND AGE&gt;=70 AND AGE&lt;=99) OR
+(LGFU='MW1' AND AGE&gt;=70 AND AGE&lt;=99) OR
+(LGFU='PJ2' AND AGE&gt;=70 AND AGE&lt;=109) OR
+(LGFU='SF1' AND AGE&gt;=80 AND AGE&lt;=109) OR
+(LGFU='MW2' AND AGE&gt;=70 AND AGE&lt;=99) OR
+(LGFU='SBOG' AND AGE&gt;=80 AND AGE&lt;=119)</t>
+  </si>
+  <si>
+    <t>(LGFU='PW1' AND AGE&gt;129) OR
+(LGFU='PR1' AND AGE&gt;129) OR
+(LGFU='PRW' AND AGE&gt;129) OR
+(LGFU='LC1' AND AGE&gt;=120) OR
+(LGFU='SB1' AND AGE&gt;=120) OR
+(LGFU='SP1' AND AGE&gt;=110) OR
+(LGFU='PJ1' AND AGE&gt;=110) OR
+(LGFU='PO1' AND AGE&gt;89) OR
+(LGFU='BW1' AND AGE&gt;89) OR
+(LGFU='LH1' AND AGE&gt;99) OR
+(LGFU='MW1' AND AGE&gt;99) OR
+(LGFU='PJ2' AND AGE&gt;109) OR
+(LGFU='SF1' AND AGE&gt;109) OR
+(LGFU='MW2' AND AGE&gt;99) OR
+(LGFU='SBOG' AND AGE&gt;=120)</t>
+  </si>
+  <si>
+    <t>(LGFU='PW1' AND AGE&gt;=0 AND AGE&lt;15) OR
+(LGFU='PR1' AND AGE&gt;0 AND AGE&lt;15) OR
+(LGFU='PRW' AND AGE&gt;=0 AND AGE&lt;15) OR
+(LGFU='LC1' AND AGE&gt;=0 AND AGE&lt;20) OR
+(LGFU='SB1' AND AGE&gt;=0 AND AGE&lt;20) OR
+(LGFU='SP1' AND AGE&gt;=0 AND AGE&lt;15) OR
+(LGFU='PJ1' AND AGE&gt;=0 AND AGE&lt;10) OR
+(LGFU='PO1' AND AGE&gt;=0 AND AGE&lt;10) OR
+(LGFU='BW1' AND AGE&gt;=0 AND AGE&lt;10) OR
+(LGFU='LH1' AND AGE&gt;=0 AND AGE&lt;10) OR
+(LGFU='MW1' AND AGE&gt;0 AND AGE&lt;10) OR
+(LGFU='PJ2' AND AGE&gt;=0 AND AGE&lt;10) OR
+(LGFU='SF1' AND AGE&gt;=0 AND AGE&lt;15) OR
+(LGFU='MW2' AND AGE&gt;=0 AND AGE&lt;10) OR
+(LGFU='SBOG' AND AGE&gt;=0 AND AGE&lt;20)</t>
+  </si>
+  <si>
+    <t>(LGFU='PW1' AND AGE&gt;=15 AND AGE&lt;=39) OR
+(LGFU='PR1' AND AGE&gt;=15 AND AGE&lt;=39) OR
+(LGFU='PRW' AND AGE&gt;=15 AND AGE&lt;=39) OR
+(LGFU='LC1' AND AGE&gt;=20 AND AGE&lt;=39) OR
+(LGFU='SB1' AND AGE&gt;=20 AND AGE&lt;=39) OR
+(LGFU='SP1' AND AGE&gt;=15 AND AGE&lt;=39) OR
+(LGFU='PJ1' AND AGE&gt;=10 AND AGE&lt;=29) OR
+(LGFU='PO1' AND AGE&gt;=10 AND AGE&lt;=29) OR
+(LGFU='BW1' AND AGE&gt;=10 AND AGE&lt;=29) OR
+(LGFU='LH1' AND AGE&gt;=10 AND AGE&lt;=29) OR
+(LGFU='MW1' AND AGE&gt;=10 AND AGE&lt;=29) OR
+(LGFU='PJ2' AND AGE&gt;=10 AND AGE&lt;=29) OR
+(LGFU='SF1' AND AGE&gt;=15 AND AGE&lt;=39) OR
+(LGFU='MW2' AND AGE&gt;=10 AND AGE&lt;=29) OR
+(LGFU='SBOG' AND AGE&gt;=20 AND AGE&lt;=39)</t>
+  </si>
+  <si>
+    <t>(LGFU='PW1' AND AGE&gt;=40 AND AGE&lt;=79) OR
+(LGFU='PR1' AND AGE&gt;=40 AND AGE&lt;=79) OR
+(LGFU='PRW' AND AGE&gt;=40 AND AGE&lt;=79) OR
+(LGFU='LC1' AND AGE&gt;=40 AND AGE&lt;=79) OR
+(LGFU='SB1' AND AGE&gt;=40 AND AGE&lt;=79) OR
+(LGFU='SP1' AND AGE&gt;=40 AND AGE&lt;=79) OR
+(LGFU='PJ1' AND AGE&gt;=30 AND AGE&lt;=69) OR
+(LGFU='PO1' AND AGE&gt;=30 AND AGE&lt;=59) OR
+(LGFU='BW1' AND AGE&gt;=30 AND AGE&lt;=69) OR
+(LGFU='LH1' AND AGE&gt;=30 AND AGE&lt;=69) OR
+(LGFU='MW1' AND AGE&gt;=30 AND AGE&lt;=69) OR
+(LGFU='PJ2' AND AGE&gt;=30 AND AGE&lt;=69) OR
+(LGFU='SF1' AND AGE&gt;=40 AND AGE&lt;=79) OR
+(LGFU='MW2' AND AGE&gt;=30 AND AGE&lt;=69) OR
+(LGFU='SBOG' AND AGE&gt;=40 AND AGE&lt;=79)</t>
+  </si>
+  <si>
+    <t>changed Bog to SBOG</t>
   </si>
 </sst>
 </file>
@@ -2587,13 +2590,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3435,10 +3438,10 @@
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="H6" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -3618,7 +3621,7 @@
         <v>86</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="375" x14ac:dyDescent="0.25">
@@ -3638,7 +3641,7 @@
         <v>103</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="375" x14ac:dyDescent="0.25">
@@ -3658,7 +3661,7 @@
         <v>120</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="375" x14ac:dyDescent="0.25">
@@ -3678,7 +3681,7 @@
         <v>137</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="375" x14ac:dyDescent="0.25">
@@ -3698,7 +3701,7 @@
         <v>154</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -5085,10 +5088,10 @@
         <v>16</v>
       </c>
       <c r="F87" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="H87" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="I87" t="s">
         <v>612</v>
@@ -5108,10 +5111,13 @@
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>336</v>
+        <v>565</v>
       </c>
       <c r="F88" t="s">
-        <v>337</v>
+        <v>717</v>
+      </c>
+      <c r="H88" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -5291,10 +5297,10 @@
         <v>137</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="G97" t="s">
-        <v>643</v>
+        <v>718</v>
+      </c>
+      <c r="H97" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="225" x14ac:dyDescent="0.25">
@@ -5314,10 +5320,10 @@
         <v>154</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="G98" t="s">
-        <v>643</v>
+        <v>719</v>
+      </c>
+      <c r="H98" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="225" x14ac:dyDescent="0.25">
@@ -5337,10 +5343,10 @@
         <v>86</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="G99" t="s">
-        <v>643</v>
+        <v>720</v>
+      </c>
+      <c r="H99" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="225" x14ac:dyDescent="0.25">
@@ -5360,10 +5366,10 @@
         <v>103</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="G100" t="s">
-        <v>643</v>
+        <v>721</v>
+      </c>
+      <c r="H100" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="225" x14ac:dyDescent="0.25">
@@ -5383,10 +5389,10 @@
         <v>120</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G101" t="s">
-        <v>643</v>
+        <v>722</v>
+      </c>
+      <c r="H101" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -5406,10 +5412,10 @@
         <v>212</v>
       </c>
       <c r="F102" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="I102" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -5429,10 +5435,10 @@
         <v>214</v>
       </c>
       <c r="F103" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="I103" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
@@ -5455,7 +5461,7 @@
         <v>604</v>
       </c>
       <c r="I104" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -5472,13 +5478,16 @@
         <v>4</v>
       </c>
       <c r="E105" t="s">
-        <v>218</v>
+        <v>565</v>
       </c>
       <c r="F105" t="s">
-        <v>700</v>
+        <v>694</v>
+      </c>
+      <c r="H105" t="s">
+        <v>723</v>
       </c>
       <c r="I105" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
@@ -5498,10 +5507,10 @@
         <v>220</v>
       </c>
       <c r="F106" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="I106" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -5521,10 +5530,10 @@
         <v>222</v>
       </c>
       <c r="F107" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="I107" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
@@ -5544,10 +5553,10 @@
         <v>224</v>
       </c>
       <c r="F108" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="I108" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
@@ -5567,10 +5576,10 @@
         <v>226</v>
       </c>
       <c r="F109" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="I109" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
@@ -5590,10 +5599,10 @@
         <v>228</v>
       </c>
       <c r="F110" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="I110" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -5610,10 +5619,10 @@
         <v>230</v>
       </c>
       <c r="F111" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="I111" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -5630,10 +5639,10 @@
         <v>232</v>
       </c>
       <c r="F112" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="I112" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -5650,10 +5659,10 @@
         <v>234</v>
       </c>
       <c r="F113" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="I113" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -5670,10 +5679,10 @@
         <v>236</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="I114" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -5690,10 +5699,10 @@
         <v>241</v>
       </c>
       <c r="F115" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="I115" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -5739,7 +5748,7 @@
         <v>352</v>
       </c>
       <c r="G117" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -5759,13 +5768,13 @@
         <v>196</v>
       </c>
       <c r="F118" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G118" t="s">
+        <v>677</v>
+      </c>
+      <c r="H118" t="s">
         <v>683</v>
-      </c>
-      <c r="H118" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -5788,7 +5797,7 @@
         <v>602</v>
       </c>
       <c r="G119" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
@@ -5811,7 +5820,7 @@
         <v>603</v>
       </c>
       <c r="G120" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -5880,7 +5889,7 @@
         <v>604</v>
       </c>
       <c r="G123" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -5906,7 +5915,7 @@
         <v>571</v>
       </c>
       <c r="I124" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -5929,10 +5938,10 @@
         <v>572</v>
       </c>
       <c r="H125" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="I125" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -5958,10 +5967,10 @@
         <v>573</v>
       </c>
       <c r="H126" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="I126" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -5981,16 +5990,16 @@
         <v>216</v>
       </c>
       <c r="F127" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="G127" t="s">
         <v>574</v>
       </c>
       <c r="H127" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="I127" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -6013,10 +6022,10 @@
         <v>575</v>
       </c>
       <c r="H128" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="I128" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
@@ -6042,10 +6051,10 @@
         <v>587</v>
       </c>
       <c r="H129" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="I129" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
@@ -6065,16 +6074,16 @@
         <v>220</v>
       </c>
       <c r="F130" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="G130" t="s">
         <v>576</v>
       </c>
       <c r="H130" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="I130" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
@@ -6094,16 +6103,16 @@
         <v>222</v>
       </c>
       <c r="F131" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="G131" t="s">
         <v>577</v>
       </c>
       <c r="H131" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="I131" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
@@ -6129,10 +6138,10 @@
         <v>578</v>
       </c>
       <c r="H132" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="I132" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
@@ -6146,19 +6155,19 @@
         <v>10</v>
       </c>
       <c r="E133" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="F133" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="G133" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="H133" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="I133" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
@@ -6184,10 +6193,10 @@
         <v>577</v>
       </c>
       <c r="H134" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="I134" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
@@ -6213,10 +6222,10 @@
         <v>579</v>
       </c>
       <c r="H135" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="I135" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
@@ -6242,10 +6251,10 @@
         <v>580</v>
       </c>
       <c r="H136" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="I136" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
@@ -6271,10 +6280,10 @@
         <v>581</v>
       </c>
       <c r="H137" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="I137" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
@@ -6300,10 +6309,10 @@
         <v>582</v>
       </c>
       <c r="H138" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="I138" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
@@ -6323,16 +6332,16 @@
         <v>583</v>
       </c>
       <c r="F139" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="G139" t="s">
         <v>588</v>
       </c>
       <c r="H139" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="I139" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
@@ -6352,16 +6361,16 @@
         <v>584</v>
       </c>
       <c r="F140" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="G140" t="s">
         <v>589</v>
       </c>
       <c r="H140" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="I140" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
@@ -6387,7 +6396,7 @@
         <v>590</v>
       </c>
       <c r="I141" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
@@ -6413,7 +6422,7 @@
         <v>591</v>
       </c>
       <c r="I142" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
@@ -6525,10 +6534,10 @@
         <v>16</v>
       </c>
       <c r="F147" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="H147" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
@@ -6568,10 +6577,10 @@
         <v>179</v>
       </c>
       <c r="F149" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="H149" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
@@ -6591,10 +6600,10 @@
         <v>181</v>
       </c>
       <c r="F150" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="H150" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
@@ -6614,10 +6623,10 @@
         <v>183</v>
       </c>
       <c r="F151" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="H151" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
@@ -6637,7 +6646,7 @@
         <v>185</v>
       </c>
       <c r="F152" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
@@ -6657,7 +6666,7 @@
         <v>187</v>
       </c>
       <c r="F153" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
@@ -6677,10 +6686,10 @@
         <v>189</v>
       </c>
       <c r="F154" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="H154" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="240" x14ac:dyDescent="0.25">
@@ -6697,10 +6706,10 @@
         <v>86</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="H155" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="240" x14ac:dyDescent="0.25">
@@ -6720,7 +6729,7 @@
         <v>103</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="240" x14ac:dyDescent="0.25">
@@ -6740,7 +6749,7 @@
         <v>120</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="240" x14ac:dyDescent="0.25">
@@ -6760,10 +6769,10 @@
         <v>137</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="H158" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="240" x14ac:dyDescent="0.25">
@@ -6783,7 +6792,7 @@
         <v>154</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
@@ -7166,7 +7175,7 @@
         <v>201</v>
       </c>
       <c r="I178" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
@@ -7315,7 +7324,7 @@
         <v>25</v>
       </c>
       <c r="F185" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I185" t="s">
         <v>619</v>
@@ -17524,14 +17533,14 @@
         <v>216</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="F5" s="10"/>
       <c r="G5" s="10" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -17588,12 +17597,12 @@
         <v>220</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="8" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -17610,14 +17619,14 @@
         <v>222</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="10" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -17634,12 +17643,12 @@
         <v>224</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="8" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -17696,11 +17705,11 @@
         <v>228</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="10" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="H13" s="11"/>
     </row>
@@ -17738,12 +17747,12 @@
         <v>232</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="11" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -17760,12 +17769,12 @@
         <v>234</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="8" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="90" x14ac:dyDescent="0.25">
@@ -17782,14 +17791,14 @@
         <v>236</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="10" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
